--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1013"/>
+  <dimension ref="A1:Y1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57001,14 +57001,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 53925-2023</t>
+          <t>A 54019-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57058,14 +57058,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 54019-2023</t>
+          <t>A 53925-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57115,14 +57115,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 54252-2023</t>
+          <t>A 54211-2023</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57172,14 +57172,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 54211-2023</t>
+          <t>A 54217-2023</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57229,14 +57229,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 54217-2023</t>
+          <t>A 54221-2023</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57286,14 +57286,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 54221-2023</t>
+          <t>A 54252-2023</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57350,7 +57350,7 @@
         <v>45233</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45234</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57469,7 +57469,7 @@
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57809,14 +57809,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 56481-2023</t>
+          <t>A 56496-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,14 +57866,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 56496-2023</t>
+          <t>A 56481-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58037,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58056,8 +58056,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G990" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58094,14 +58099,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58113,13 +58118,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F991" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G991" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58156,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58175,13 +58175,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F992" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G992" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58218,14 +58213,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58237,13 +58232,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F993" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G993" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58280,14 +58270,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58300,7 +58290,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58337,14 +58327,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58356,8 +58346,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G995" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58394,14 +58389,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58413,8 +58408,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G996" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58451,14 +58451,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58513,14 +58513,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58582,7 +58582,7 @@
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58644,7 +58644,7 @@
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58984,14 +58984,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 58645-2023</t>
+          <t>A 58659-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -59046,14 +59046,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 58659-2023</t>
+          <t>A 58645-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -59115,7 +59115,7 @@
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59222,14 +59222,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 59759-2023</t>
+          <t>A 59769-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59279,14 +59279,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 59769-2023</t>
+          <t>A 59759-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59343,7 +59343,7 @@
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
       </c>
       <c r="R1012" s="2" t="inlineStr"/>
     </row>
-    <row r="1013">
+    <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
           <t>A 59989-2023</t>
@@ -59400,7 +59400,7 @@
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59446,6 +59446,63 @@
         <v>0</v>
       </c>
       <c r="R1013" s="2" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>A 60278-2023</t>
+        </is>
+      </c>
+      <c r="B1014" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C1014" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1014" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57001,14 +57001,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 54019-2023</t>
+          <t>A 53925-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57058,14 +57058,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 53925-2023</t>
+          <t>A 54019-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45233</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45234</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57462,14 +57462,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 54831-2023</t>
+          <t>A 54895-2023</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57519,14 +57519,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 54895-2023</t>
+          <t>A 54920-2023</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57576,14 +57576,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 54920-2023</t>
+          <t>A 54831-2023</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58037,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58056,13 +58056,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F990" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G990" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58099,14 +58094,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58118,8 +58113,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G991" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58156,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58213,14 +58213,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58232,8 +58232,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G993" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58270,14 +58275,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58289,8 +58294,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G994" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58327,14 +58337,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58346,13 +58356,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F995" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G995" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58389,14 +58394,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58408,13 +58413,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F996" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G996" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58451,14 +58451,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58513,14 +58513,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58575,14 +58575,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 57523-2023</t>
+          <t>A 57599-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58594,13 +58594,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F999" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G999" t="n">
-        <v>12.6</v>
+        <v>0.7</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58637,14 +58632,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 57599-2023</t>
+          <t>A 57615-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58656,8 +58651,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G1000" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58694,14 +58694,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 57615-2023</t>
+          <t>A 57523-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59222,14 +59222,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 59769-2023</t>
+          <t>A 59759-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59279,14 +59279,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 59759-2023</t>
+          <t>A 59769-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59343,7 +59343,7 @@
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1014"/>
+  <dimension ref="A1:Y1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57001,14 +57001,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 53925-2023</t>
+          <t>A 54019-2023</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57058,14 +57058,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 54019-2023</t>
+          <t>A 53925-2023</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57078,7 +57078,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57115,14 +57115,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 54211-2023</t>
+          <t>A 54252-2023</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57172,14 +57172,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 54217-2023</t>
+          <t>A 54211-2023</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57229,14 +57229,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 54221-2023</t>
+          <t>A 54217-2023</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57286,14 +57286,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 54252-2023</t>
+          <t>A 54221-2023</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57350,7 +57350,7 @@
         <v>45233</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45234</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57462,14 +57462,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 54895-2023</t>
+          <t>A 54920-2023</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57519,14 +57519,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 54920-2023</t>
+          <t>A 54831-2023</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57576,14 +57576,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 54831-2023</t>
+          <t>A 54895-2023</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57809,14 +57809,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 56496-2023</t>
+          <t>A 56481-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,14 +57866,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 56481-2023</t>
+          <t>A 56496-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58037,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58094,14 +58094,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58156,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58220,7 +58220,7 @@
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58282,7 +58282,7 @@
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58337,14 +58337,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58356,8 +58356,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G995" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58394,14 +58399,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58413,8 +58418,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G996" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58451,14 +58461,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58470,13 +58480,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F997" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G997" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58513,14 +58518,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58532,13 +58537,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F998" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G998" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58582,7 +58582,7 @@
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59108,14 +59108,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 59192-2023</t>
+          <t>A 59278-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -59165,14 +59165,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 59278-2023</t>
+          <t>A 59192-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59229,7 +59229,7 @@
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
       </c>
       <c r="R1013" s="2" t="inlineStr"/>
     </row>
-    <row r="1014">
+    <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
           <t>A 60278-2023</t>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59503,6 +59503,63 @@
         <v>0</v>
       </c>
       <c r="R1014" s="2" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>A 60872-2023</t>
+        </is>
+      </c>
+      <c r="B1015" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1015" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1015" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1015"/>
+  <dimension ref="A1:Y1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57115,14 +57115,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 54252-2023</t>
+          <t>A 54211-2023</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57172,14 +57172,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 54211-2023</t>
+          <t>A 54217-2023</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57229,14 +57229,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 54217-2023</t>
+          <t>A 54221-2023</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57286,14 +57286,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 54221-2023</t>
+          <t>A 54252-2023</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57350,7 +57350,7 @@
         <v>45233</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45234</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57469,7 +57469,7 @@
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57809,14 +57809,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 56481-2023</t>
+          <t>A 56496-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,14 +57866,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 56496-2023</t>
+          <t>A 56481-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58044,7 +58044,7 @@
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58156,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58175,8 +58175,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G992" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58213,14 +58218,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58238,7 +58243,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58275,14 +58280,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58294,13 +58299,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F994" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G994" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58337,14 +58337,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58399,14 +58399,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58418,13 +58418,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F996" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G996" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58461,14 +58456,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58481,7 +58476,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58518,14 +58513,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58537,8 +58532,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G998" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58575,14 +58575,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 57599-2023</t>
+          <t>A 57523-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58594,8 +58594,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G999" t="n">
-        <v>0.7</v>
+        <v>12.6</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58632,14 +58637,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 57615-2023</t>
+          <t>A 57599-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58651,13 +58656,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F1000" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G1000" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58694,14 +58694,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 57523-2023</t>
+          <t>A 57615-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>12.6</v>
+        <v>3.9</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59222,14 +59222,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 59759-2023</t>
+          <t>A 59769-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59279,14 +59279,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 59769-2023</t>
+          <t>A 59759-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59336,14 +59336,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 59770-2023</t>
+          <t>A 59989-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -59393,14 +59393,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 59989-2023</t>
+          <t>A 59770-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
       </c>
       <c r="R1014" s="2" t="inlineStr"/>
     </row>
-    <row r="1015">
+    <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
           <t>A 60872-2023</t>
@@ -59514,7 +59514,7 @@
         <v>45261</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59560,6 +59560,234 @@
         <v>0</v>
       </c>
       <c r="R1015" s="2" t="inlineStr"/>
+    </row>
+    <row r="1016" ht="15" customHeight="1">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>A 60884-2023</t>
+        </is>
+      </c>
+      <c r="B1016" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1016" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1016" s="2" t="inlineStr"/>
+    </row>
+    <row r="1017" ht="15" customHeight="1">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>A 60893-2023</t>
+        </is>
+      </c>
+      <c r="B1017" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1017" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1017" s="2" t="inlineStr"/>
+    </row>
+    <row r="1018" ht="15" customHeight="1">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>A 60887-2023</t>
+        </is>
+      </c>
+      <c r="B1018" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1018" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1018" s="2" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>A 61104-2023</t>
+        </is>
+      </c>
+      <c r="B1019" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1019" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1019" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57343,14 +57343,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 54441-2023</t>
+          <t>A 54619-2023</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
-        <v>45233</v>
+        <v>45234</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57362,13 +57362,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F978" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G978" t="n">
-        <v>5.5</v>
+        <v>10.3</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57405,14 +57400,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 54619-2023</t>
+          <t>A 54441-2023</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
-        <v>45234</v>
+        <v>45233</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57424,8 +57419,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G979" t="n">
-        <v>10.3</v>
+        <v>5.5</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57462,14 +57462,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 54920-2023</t>
+          <t>A 54831-2023</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57519,14 +57519,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 54831-2023</t>
+          <t>A 54920-2023</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57583,7 +57583,7 @@
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57809,14 +57809,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 56496-2023</t>
+          <t>A 56481-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,14 +57866,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 56481-2023</t>
+          <t>A 56496-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -57999,8 +57999,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G989" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58037,14 +58042,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58056,8 +58061,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G990" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58094,14 +58104,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58113,13 +58123,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F991" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G991" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58156,14 +58161,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58181,7 +58186,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58218,14 +58223,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58237,13 +58242,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F993" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G993" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58280,14 +58280,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58337,14 +58337,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58399,14 +58399,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58418,8 +58418,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G996" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58456,14 +58461,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58476,7 +58481,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58513,14 +58518,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58532,13 +58537,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F998" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G998" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58582,7 +58582,7 @@
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58644,7 +58644,7 @@
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58984,14 +58984,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 58659-2023</t>
+          <t>A 58645-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -59046,14 +59046,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 58645-2023</t>
+          <t>A 58659-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -59108,14 +59108,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 59278-2023</t>
+          <t>A 59192-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -59165,14 +59165,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 59192-2023</t>
+          <t>A 59278-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59229,7 +59229,7 @@
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45261</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59564,14 +59564,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 60884-2023</t>
+          <t>A 60887-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45261</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59678,14 +59678,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 60887-2023</t>
+          <t>A 60884-2023</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>45261</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45234</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45233</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57462,14 +57462,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 54831-2023</t>
+          <t>A 54920-2023</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57519,14 +57519,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 54920-2023</t>
+          <t>A 54895-2023</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57576,14 +57576,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 54895-2023</t>
+          <t>A 54831-2023</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -57999,13 +57999,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F989" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G989" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58042,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58067,7 +58062,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58104,14 +58099,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58123,8 +58118,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G991" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58161,14 +58161,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58180,13 +58180,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F992" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G992" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58223,14 +58218,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58243,7 +58238,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58280,14 +58275,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58299,8 +58294,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G994" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58337,14 +58337,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58399,14 +58399,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58461,14 +58461,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58525,7 +58525,7 @@
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58644,7 +58644,7 @@
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59108,14 +59108,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 59192-2023</t>
+          <t>A 59278-2023</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -59165,14 +59165,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 59278-2023</t>
+          <t>A 59192-2023</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59222,14 +59222,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 59769-2023</t>
+          <t>A 59759-2023</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59279,14 +59279,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 59759-2023</t>
+          <t>A 59769-2023</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59336,14 +59336,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 59989-2023</t>
+          <t>A 59770-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -59393,14 +59393,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 59770-2023</t>
+          <t>A 59989-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45261</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59564,14 +59564,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 60887-2023</t>
+          <t>A 60893-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -59621,14 +59621,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 60893-2023</t>
+          <t>A 60887-2023</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -59685,7 +59685,7 @@
         <v>45261</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>45261</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45234</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45233</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57469,7 +57469,7 @@
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57519,14 +57519,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 54895-2023</t>
+          <t>A 54831-2023</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57576,14 +57576,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 54831-2023</t>
+          <t>A 54895-2023</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57809,14 +57809,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 56481-2023</t>
+          <t>A 56496-2023</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>9.9</v>
+        <v>6</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,14 +57866,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 56496-2023</t>
+          <t>A 56481-2023</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58037,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58099,14 +58099,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57136-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58118,13 +58118,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F991" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G991" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58161,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58181,7 +58176,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58218,14 +58213,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58238,7 +58233,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58275,14 +58270,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57132-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58294,13 +58289,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F994" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G994" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58337,14 +58327,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57138-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58362,7 +58352,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58399,14 +58389,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57136-2023</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58424,7 +58414,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58461,14 +58451,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57132-2023</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58480,8 +58470,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G997" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58518,14 +58513,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57138-2023</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58537,8 +58532,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G998" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58575,14 +58575,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 57523-2023</t>
+          <t>A 57599-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58594,13 +58594,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F999" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G999" t="n">
-        <v>12.6</v>
+        <v>0.7</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58637,14 +58632,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 57599-2023</t>
+          <t>A 57615-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58656,8 +58651,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G1000" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58694,14 +58694,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 57615-2023</t>
+          <t>A 57523-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58984,14 +58984,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 58645-2023</t>
+          <t>A 58659-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -59046,14 +59046,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 58659-2023</t>
+          <t>A 58645-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -59115,7 +59115,7 @@
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45261</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>45261</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45261</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45261</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>45261</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1019"/>
+  <dimension ref="A1:Y1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45234</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45233</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57469,7 +57469,7 @@
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57980,14 +57980,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 57112-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58037,14 +58037,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 57125-2023</t>
+          <t>A 57112-2023</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58056,13 +58056,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F990" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G990" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58099,14 +58094,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 57141-2023</t>
+          <t>A 57125-2023</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58118,8 +58113,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G991" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58156,14 +58156,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 57221-2023</t>
+          <t>A 57141-2023</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58213,14 +58213,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57221-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58277,7 +58277,7 @@
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58820,7 +58820,7 @@
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58877,7 +58877,7 @@
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58984,14 +58984,14 @@
     <row r="1006" ht="15" customHeight="1">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>A 58659-2023</t>
+          <t>A 58645-2023</t>
         </is>
       </c>
       <c r="B1006" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -59046,14 +59046,14 @@
     <row r="1007" ht="15" customHeight="1">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>A 58645-2023</t>
+          <t>A 58659-2023</t>
         </is>
       </c>
       <c r="B1007" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="H1007" t="n">
         <v>0</v>
@@ -59115,7 +59115,7 @@
         <v>45253</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45253</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>45254</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45254</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59336,14 +59336,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 59770-2023</t>
+          <t>A 59989-2023</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -59393,14 +59393,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 59989-2023</t>
+          <t>A 59770-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -59457,7 +59457,7 @@
         <v>45258</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45261</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>45261</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45261</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45261</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
       </c>
       <c r="R1018" s="2" t="inlineStr"/>
     </row>
-    <row r="1019">
+    <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
           <t>A 61104-2023</t>
@@ -59742,7 +59742,7 @@
         <v>45261</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59788,6 +59788,177 @@
         <v>0</v>
       </c>
       <c r="R1019" s="2" t="inlineStr"/>
+    </row>
+    <row r="1020" ht="15" customHeight="1">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>A 61546-2023</t>
+        </is>
+      </c>
+      <c r="B1020" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1020" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1020" s="2" t="inlineStr"/>
+    </row>
+    <row r="1021" ht="15" customHeight="1">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>A 61549-2023</t>
+        </is>
+      </c>
+      <c r="B1021" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1021" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1021" s="2" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>A 61545-2023</t>
+        </is>
+      </c>
+      <c r="B1022" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C1022" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>EDA</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1022" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45021</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45029</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45029</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45029</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45029</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45029</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45029</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45030</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45035</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45036</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45040</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45041</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45041</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45041</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45050</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45051</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45054</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45054</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45054</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45054</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45055</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45058</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45058</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45061</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45061</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45062</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45063</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45063</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45069</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45069</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45070</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45071</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45071</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45071</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45071</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45076</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45076</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45083</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45084</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45084</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45084</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45085</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45086</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45086</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45087</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45087</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45087</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45089</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45090</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45090</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>45090</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>45090</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45090</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45090</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45090</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45090</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45091</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45091</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45091</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45091</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45091</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45091</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45091</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45092</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45092</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45092</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45092</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45093</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45093</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45093</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45096</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45098</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45098</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45099</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45099</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45104</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45104</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45105</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45105</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45106</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45106</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45107</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45107</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45110</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45110</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>45110</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45111</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45111</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45114</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49615,7 +49615,7 @@
         <v>45114</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45114</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45114</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45119</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45128</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45131</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45134</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45135</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45135</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45135</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45139</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45140</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45140</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45140</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45140</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45142</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45142</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>45145</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>45145</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45145</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>45145</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>45146</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>45148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>45149</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45152</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45152</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45152</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45153</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45153</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45153</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45154</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45155</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45156</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45156</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45159</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45161</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>45161</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45161</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45161</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45161</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45162</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45162</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45162</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45166</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45166</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45167</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45167</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45168</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45168</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45173</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45173</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>45173</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45173</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45173</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45175</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45176</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45176</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45176</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45176</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45178</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45180</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45181</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45182</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45183</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45184</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45184</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45184</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45184</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45187</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45187</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45188</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45189</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45191</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45191</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45192</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45194</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>45194</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45195</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45195</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45196</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45196</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>45196</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45197</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45197</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45197</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45197</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45202</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45203</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45203</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45203</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45203</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45204</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45204</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45204</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45204</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45206</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45209</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45209</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45210</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45210</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45210</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45214</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45215</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>45218</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56066,7 +56066,7 @@
         <v>45218</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45221</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45221</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45221</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45222</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45223</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45224</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45224</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45226</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45226</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45229</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45229</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45231</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45231</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45234</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45233</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57469,7 +57469,7 @@
         <v>45236</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45236</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>45236</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45237</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45238</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45239</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45243</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45243</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>45244</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57987,7 +57987,7 @@
         <v>45245</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58044,7 +58044,7 @@
         <v>45245</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>45245</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58163,7 +58163,7 @@
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58213,14 +58213,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 57115-2023</t>
+          <t>A 57113-2023</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58270,14 +58270,14 @@
     <row r="994" ht="15" customHeight="1">
       <c r="A994" t="inlineStr">
         <is>
-          <t>A 57113-2023</t>
+          <t>A 57121-2023</t>
         </is>
       </c>
       <c r="B994" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58289,8 +58289,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G994" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H994" t="n">
         <v>0</v>
@@ -58327,14 +58332,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 57121-2023</t>
+          <t>A 57115-2023</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58346,13 +58351,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F995" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G995" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58396,7 +58396,7 @@
         <v>45245</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>45245</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>45245</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58575,14 +58575,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 57523-2023</t>
+          <t>A 57599-2023</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58594,13 +58594,8 @@
           <t>EDA</t>
         </is>
       </c>
-      <c r="F999" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G999" t="n">
-        <v>12.6</v>
+        <v>0.7</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58637,14 +58632,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 57599-2023</t>
+          <t>A 57615-2023</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58656,8 +58651,13 @@
           <t>EDA</t>
         </is>
       </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G1000" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58694,14 +58694,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 57615-2023</t>
+          <t>A 57523-2023</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -58763,7 +58763,7 @@
         <v>45247</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58813,14 +58813,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 58344-2023</t>
+          <t>A 58174-2023</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -58870,14 +58870,14 @@
     <row r="1004" ht="15" customHeight="1">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>A 58174-2023</t>
+          <t>A 58179-2023</t>
         </is>
       </c>
       <c r="B1004" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -58927,14 +58927,14 @@
     <row r="1005" ht="15" customHeight="1">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>A 58179-2023</t>
+          <t>A 58344-2023</t>
         </is>
       </c>
       <c r="B1005" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58947,7 +58947,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H1005" t="n">
         <v>0</v>
@@ -58991,7 +58991,7 @@
         <v>45251</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45251</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>45252</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45252</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>45252</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45253</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45253</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59393,14 +59393,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 59769-2023</t>
+          <t>A 59759-2023</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -59450,14 +59450,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 59759-2023</t>
+          <t>A 59769-2023</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -59507,14 +59507,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 59989-2023</t>
+          <t>A 59770-2023</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -59564,14 +59564,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 59770-2023</t>
+          <t>A 59989-2023</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -59628,7 +59628,7 @@
         <v>45258</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45261</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59735,14 +59735,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 60884-2023</t>
+          <t>A 60887-2023</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45261</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59849,14 +59849,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 61104-2023</t>
+          <t>A 60884-2023</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -59906,14 +59906,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 60887-2023</t>
+          <t>A 61104-2023</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -59963,14 +59963,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 61549-2023</t>
+          <t>A 61545-2023</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -60027,7 +60027,7 @@
         <v>45265</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60077,14 +60077,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 61545-2023</t>
+          <t>A 61549-2023</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45265</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -60141,7 +60141,7 @@
         <v>45266</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60191,14 +60191,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 62183-2023</t>
+          <t>A 62173-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -60248,14 +60248,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 62173-2023</t>
+          <t>A 62324-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -60305,14 +60305,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 62324-2023</t>
+          <t>A 62332-2023</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -60362,14 +60362,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 62332-2023</t>
+          <t>A 62174-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -60419,14 +60419,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 62174-2023</t>
+          <t>A 62183-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -60483,7 +60483,7 @@
         <v>45267</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -564,7 +564,7 @@
         <v>43418</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>43423</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>44494</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>43483</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>43418</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44375</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>45243</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>43418</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44375</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44740</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44791</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44930</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>43418</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44296</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44865</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>44868</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44881</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>43376</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>43418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>43419</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>43419</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>43496</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>43766</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44377</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44452</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44970</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45243</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43335</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43335</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43348</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43353</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43369</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>43374</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>43376</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>43376</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>43382</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>43387</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>43388</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>43391</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>43395</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>43397</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>43412</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>43412</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>43412</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>43415</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>43418</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>43418</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>43419</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>43419</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>43419</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>43422</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>43426</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>43427</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>43431</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>43432</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>43434</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>43439</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>43441</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>43441</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>43442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>43442</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>43442</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43444</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>43446</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>43451</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>43451</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43452</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43468</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43473</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43474</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43474</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43475</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43475</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43482</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43482</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43488</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43493</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43497</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43504</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43517</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43521</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43523</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43524</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43535</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43539</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43542</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43543</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43544</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43550</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43551</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43551</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43552</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43554</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43558</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>43559</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>43560</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43563</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43565</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43570</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43570</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43572</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43572</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43573</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43580</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43584</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43584</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43584</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>43584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43588</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43588</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>43589</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>43589</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>43598</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>43600</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>43606</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>43606</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43608</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43609</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43621</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43635</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43653</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43661</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43668</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43668</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43668</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43671</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43671</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43683</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43685</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43685</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>43685</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>43685</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>43688</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>43688</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>43690</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>43690</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>43690</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>43690</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>43692</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>43703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>43704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>43705</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>43710</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>43713</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>43717</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>43717</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>43718</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>43718</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>43724</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>43725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>43725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>43725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>43739</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>43747</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>43755</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>43755</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43755</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>43761</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>43762</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>43763</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43763</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43763</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43766</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43766</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43768</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>43768</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>43769</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43770</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43770</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>43770</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>43770</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>43772</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>43774</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>43777</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>43777</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>43784</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>43784</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>43787</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43789</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43794</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43795</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43795</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43810</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43811</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43811</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43811</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43819</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43819</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>43826</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>43833</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43840</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43840</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43843</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43843</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43843</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43844</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>43844</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>43850</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>43857</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>43858</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>43867</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>43867</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>43871</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>43872</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>43872</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>43872</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>43880</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>43885</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>43886</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>43888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>43892</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>43895</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>43896</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>43901</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>43902</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>43906</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>43907</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43907</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43907</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>43908</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43914</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43920</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43921</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43921</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43924</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43930</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>43936</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43949</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>43949</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>43977</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>43985</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43993</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43997</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43999</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44004</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44007</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44008</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44019</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44020</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44021</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44025</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44030</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44030</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44040</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44041</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44042</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44047</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44048</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>44050</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44053</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44054</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44056</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44057</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44062</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44062</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44064</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44067</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44067</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44068</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44069</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44069</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44077</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44083</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44083</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44085</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>44099</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>44109</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44110</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44110</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44110</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44117</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44127</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44131</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44131</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44131</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44131</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44131</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44133</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>44133</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44134</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44137</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44144</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44144</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44144</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>44148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44151</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44162</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44166</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44166</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44166</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44169</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44173</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44175</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44175</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44179</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44179</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44182</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44182</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44186</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44201</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44207</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44207</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>44217</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>44217</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44217</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44223</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44224</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44225</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44227</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44227</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44227</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44235</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44236</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44244</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44244</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44244</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44244</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44244</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44249</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44257</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44271</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44278</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44281</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44285</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44286</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44286</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44288</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44288</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44290</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44290</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44290</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44298</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44320</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44326</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44327</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44327</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44329</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44329</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44329</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44329</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44329</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44335</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44337</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44342</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44350</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44351</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44356</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44356</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44357</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44357</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44357</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44369</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44369</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44369</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44375</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44376</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44377</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44377</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44377</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44383</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44385</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>44386</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44403</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44404</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44410</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44410</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44412</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44413</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44413</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44419</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44419</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>44420</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44426</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44426</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44426</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44426</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44427</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44433</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44438</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44439</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44439</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44442</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44442</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44445</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44445</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44451</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44463</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>44467</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44469</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44470</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44470</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44474</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44474</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44476</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44476</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44476</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44477</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44479</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44479</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44483</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44491</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44491</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44494</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44494</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44502</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44503</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44505</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44505</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44515</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44515</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44517</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44517</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44523</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44523</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44523</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44529</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44529</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44529</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44532</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44538</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>44538</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44543</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44546</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44546</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44551</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44557</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44557</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44560</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44564</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44566</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44566</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44573</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>44573</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44575</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>44582</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44581</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44582</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44582</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44584</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44585</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44586</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44586</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44588</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44588</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44595</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44602</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44602</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44602</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44608</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44610</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44619</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44625</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44627</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44629</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>44636</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44648</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44655</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44656</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44659</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44659</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44662</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44665</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44670</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44671</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44677</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44678</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44683</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44683</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44685</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44692</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44692</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44693</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>44694</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44698</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44700</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44705</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44712</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44712</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>44714</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44714</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44719</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44719</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44722</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44740</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44740</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44743</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44746</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44746</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44750</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44762</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44769</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44774</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44776</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44777</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44781</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44781</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44781</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44786</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44790</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44797</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44797</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44798</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>44798</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44799</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44799</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44799</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44799</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44804</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44806</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44806</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44816</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44817</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44818</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44820</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44820</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44831</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44834</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44837</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44839</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44840</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44840</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44845</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44851</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44851</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44853</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>44857</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44857</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44858</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44858</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44860</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44861</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44865</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44865</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44867</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44872</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44872</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44872</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44872</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44872</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44874</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>44874</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44874</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44874</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44874</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44874</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44877</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44879</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>44881</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44881</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44883</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>44883</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44896</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44896</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44896</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44899</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44899</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44901</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44901</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44901</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44901</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44901</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44904</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44909</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44911</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44915</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44915</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>44915</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44916</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>44916</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44917</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>44918</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44918</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44925</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44925</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44925</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44928</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>44930</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>44935</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44935</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44937</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>44937</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>44942</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44942</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44943</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>44951</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44958</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>44959</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44959</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44966</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44966</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>44977</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44979</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44979</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44979</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>44986</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44988</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44998</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44998</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44999</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45008</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45015</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45015</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45020</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45021</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45021</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43144,7 +43144